--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1281"/>
+  <dimension ref="A1:I1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41873,7 +41873,7 @@
         </is>
       </c>
       <c r="G1256" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1256" t="n">
         <v>41.605</v>
@@ -41906,7 +41906,7 @@
         </is>
       </c>
       <c r="G1257" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1257" t="n">
         <v>5526</v>
@@ -41939,7 +41939,7 @@
         </is>
       </c>
       <c r="G1258" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1258" t="n">
         <v>348.7</v>
@@ -41972,7 +41972,7 @@
         </is>
       </c>
       <c r="G1259" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1259" t="n">
         <v>40.27</v>
@@ -42005,7 +42005,7 @@
         </is>
       </c>
       <c r="G1260" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1260" t="n">
         <v>84.59999999999999</v>
@@ -42038,7 +42038,7 @@
         </is>
       </c>
       <c r="G1261" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1261" t="n">
         <v>71.76000000000001</v>
@@ -42070,9 +42070,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1262" t="inlineStr"/>
-      <c r="H1262" t="inlineStr"/>
-      <c r="I1262" t="inlineStr"/>
+      <c r="G1262" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>5498</v>
+      </c>
+      <c r="I1262" t="n">
+        <v>0.1452960406828914</v>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" s="1" t="n">
@@ -42098,7 +42104,7 @@
         </is>
       </c>
       <c r="G1263" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1263" t="n">
         <v>20.349</v>
@@ -42130,9 +42136,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1264" t="inlineStr"/>
-      <c r="H1264" t="inlineStr"/>
-      <c r="I1264" t="inlineStr"/>
+      <c r="G1264" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1264" t="n">
+        <v>3.671518574842489</v>
+      </c>
     </row>
     <row r="1265">
       <c r="A1265" s="1" t="n">
@@ -42157,9 +42169,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1265" t="inlineStr"/>
-      <c r="H1265" t="inlineStr"/>
-      <c r="I1265" t="inlineStr"/>
+      <c r="G1265" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="I1265" t="n">
+        <v>4.416706673067682</v>
+      </c>
     </row>
     <row r="1266">
       <c r="A1266" s="1" t="n">
@@ -42184,9 +42202,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1266" t="inlineStr"/>
-      <c r="H1266" t="inlineStr"/>
-      <c r="I1266" t="inlineStr"/>
+      <c r="G1266" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="I1266" t="n">
+        <v>2.029220779220779</v>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" s="1" t="n">
@@ -42211,9 +42235,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1267" t="inlineStr"/>
-      <c r="H1267" t="inlineStr"/>
-      <c r="I1267" t="inlineStr"/>
+      <c r="G1267" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>5498</v>
+      </c>
+      <c r="I1267" t="n">
+        <v>-0.5854372484449323</v>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" s="1" t="n">
@@ -42238,9 +42268,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1268" t="inlineStr"/>
-      <c r="H1268" t="inlineStr"/>
-      <c r="I1268" t="inlineStr"/>
+      <c r="G1268" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>5410.5</v>
+      </c>
+      <c r="I1268" t="n">
+        <v>-4.318904849127542</v>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" s="1" t="n">
@@ -42265,9 +42301,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1269" t="inlineStr"/>
-      <c r="H1269" t="inlineStr"/>
-      <c r="I1269" t="inlineStr"/>
+      <c r="G1269" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I1269" t="n">
+        <v>3.538536112457588</v>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" s="1" t="n">
@@ -42292,9 +42334,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1270" t="inlineStr"/>
-      <c r="H1270" t="inlineStr"/>
-      <c r="I1270" t="inlineStr"/>
+      <c r="G1270" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1270" t="n">
+        <v>1.576026637069909</v>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" s="1" t="n">
@@ -42319,9 +42367,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1271" t="inlineStr"/>
-      <c r="H1271" t="inlineStr"/>
-      <c r="I1271" t="inlineStr"/>
+      <c r="G1271" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="I1271" t="n">
+        <v>0.9364548494983197</v>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" s="1" t="n">
@@ -42346,9 +42400,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1272" t="inlineStr"/>
-      <c r="H1272" t="inlineStr"/>
-      <c r="I1272" t="inlineStr"/>
+      <c r="G1272" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>1599</v>
+      </c>
+      <c r="I1272" t="n">
+        <v>-2.29147571035747</v>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" s="1" t="n">
@@ -42373,9 +42433,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1273" t="inlineStr"/>
-      <c r="H1273" t="inlineStr"/>
-      <c r="I1273" t="inlineStr"/>
+      <c r="G1273" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="I1273" t="n">
+        <v>0.4925325707022597</v>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" s="1" t="n">
@@ -42400,9 +42466,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1274" t="inlineStr"/>
-      <c r="H1274" t="inlineStr"/>
-      <c r="I1274" t="inlineStr"/>
+      <c r="G1274" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="I1274" t="n">
+        <v>1.45114479200258</v>
+      </c>
     </row>
     <row r="1275">
       <c r="A1275" s="1" t="n">
@@ -42427,9 +42499,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1275" t="inlineStr"/>
-      <c r="H1275" t="inlineStr"/>
-      <c r="I1275" t="inlineStr"/>
+      <c r="G1275" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1275" t="n">
+        <v>-2.805786935554568</v>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" s="1" t="n">
@@ -42454,9 +42532,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1276" t="inlineStr"/>
-      <c r="H1276" t="inlineStr"/>
-      <c r="I1276" t="inlineStr"/>
+      <c r="G1276" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>285.66</v>
+      </c>
+      <c r="I1276" t="n">
+        <v>0.2315789473684298</v>
+      </c>
     </row>
     <row r="1277">
       <c r="A1277" s="1" t="n">
@@ -42481,9 +42565,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1277" t="inlineStr"/>
-      <c r="H1277" t="inlineStr"/>
-      <c r="I1277" t="inlineStr"/>
+      <c r="G1277" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="I1277" t="n">
+        <v>-0.1818181818181887</v>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" s="1" t="n">
@@ -42508,9 +42598,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1278" t="inlineStr"/>
-      <c r="H1278" t="inlineStr"/>
-      <c r="I1278" t="inlineStr"/>
+      <c r="G1278" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="I1278" t="n">
+        <v>4.308729861371308</v>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" s="1" t="n">
@@ -42535,9 +42631,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1279" t="inlineStr"/>
-      <c r="H1279" t="inlineStr"/>
-      <c r="I1279" t="inlineStr"/>
+      <c r="G1279" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>7.304</v>
+      </c>
+      <c r="I1279" t="n">
+        <v>3.93265816125213</v>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" s="1" t="n">
@@ -42562,9 +42664,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1280" t="inlineStr"/>
-      <c r="H1280" t="inlineStr"/>
-      <c r="I1280" t="inlineStr"/>
+      <c r="G1280" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>128.42</v>
+      </c>
+      <c r="I1280" t="n">
+        <v>2.962067402146</v>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" s="1" t="n">
@@ -42589,9 +42697,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1281" t="inlineStr"/>
-      <c r="H1281" t="inlineStr"/>
-      <c r="I1281" t="inlineStr"/>
+      <c r="G1281" s="1" t="n">
+        <v>46279.72194209049</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>2649.5</v>
+      </c>
+      <c r="I1281" t="n">
+        <v>-3.11344619575793</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>5542</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>5819.1</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>5264.9</v>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr"/>
+      <c r="H1282" t="inlineStr"/>
+      <c r="I1282" t="inlineStr"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>42.1155</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>38.10449999999999</v>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr"/>
+      <c r="H1283" t="inlineStr"/>
+      <c r="I1283" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>5285</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>5549.25</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>5020.75</v>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr"/>
+      <c r="H1284" t="inlineStr"/>
+      <c r="I1284" t="inlineStr"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>84.65000000000001</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>88.88250000000001</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>80.4175</v>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr"/>
+      <c r="H1285" t="inlineStr"/>
+      <c r="I1285" t="inlineStr"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr"/>
+      <c r="H1286" t="inlineStr"/>
+      <c r="I1286" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1286"/>
+  <dimension ref="A1:I1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42071,7 +42071,7 @@
         </is>
       </c>
       <c r="G1262" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1262" t="n">
         <v>5498</v>
@@ -42137,7 +42137,7 @@
         </is>
       </c>
       <c r="G1264" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1264" t="n">
         <v>22.17</v>
@@ -42170,7 +42170,7 @@
         </is>
       </c>
       <c r="G1265" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1265" t="n">
         <v>39.82</v>
@@ -42203,7 +42203,7 @@
         </is>
       </c>
       <c r="G1266" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1266" t="n">
         <v>72.42</v>
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="G1267" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1267" t="n">
         <v>5498</v>
@@ -42269,7 +42269,7 @@
         </is>
       </c>
       <c r="G1268" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1268" t="n">
         <v>5410.5</v>
@@ -42302,7 +42302,7 @@
         </is>
       </c>
       <c r="G1269" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1269" t="n">
         <v>19.9</v>
@@ -42335,7 +42335,7 @@
         </is>
       </c>
       <c r="G1270" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1270" t="n">
         <v>22.17</v>
@@ -42368,7 +42368,7 @@
         </is>
       </c>
       <c r="G1271" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1271" t="n">
         <v>59.24</v>
@@ -42401,7 +42401,7 @@
         </is>
       </c>
       <c r="G1272" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1272" t="n">
         <v>1599</v>
@@ -42434,7 +42434,7 @@
         </is>
       </c>
       <c r="G1273" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1273" t="n">
         <v>632.5</v>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="G1274" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1274" t="n">
         <v>314.6</v>
@@ -42500,7 +42500,7 @@
         </is>
       </c>
       <c r="G1275" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1275" t="n">
         <v>22.17</v>
@@ -42533,7 +42533,7 @@
         </is>
       </c>
       <c r="G1276" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1276" t="n">
         <v>285.66</v>
@@ -42566,7 +42566,7 @@
         </is>
       </c>
       <c r="G1277" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1277" t="n">
         <v>33.06</v>
@@ -42599,7 +42599,7 @@
         </is>
       </c>
       <c r="G1278" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1278" t="n">
         <v>25.54</v>
@@ -42632,7 +42632,7 @@
         </is>
       </c>
       <c r="G1279" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1279" t="n">
         <v>7.304</v>
@@ -42665,7 +42665,7 @@
         </is>
       </c>
       <c r="G1280" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1280" t="n">
         <v>128.42</v>
@@ -42698,7 +42698,7 @@
         </is>
       </c>
       <c r="G1281" s="1" t="n">
-        <v>46279.72194209049</v>
+        <v>46279.7219420949</v>
       </c>
       <c r="H1281" t="n">
         <v>2649.5</v>
@@ -42784,9 +42784,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1284" t="inlineStr"/>
-      <c r="H1284" t="inlineStr"/>
-      <c r="I1284" t="inlineStr"/>
+      <c r="G1284" s="1" t="n">
+        <v>46280.65773967267</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>5549.25</v>
+      </c>
+      <c r="I1284" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" s="1" t="n">
@@ -42841,6 +42847,249 @@
       <c r="G1286" t="inlineStr"/>
       <c r="H1286" t="inlineStr"/>
       <c r="I1286" t="inlineStr"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>VTBR</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>49.7705</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>56.5812</v>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr"/>
+      <c r="H1287" t="inlineStr"/>
+      <c r="I1287" t="inlineStr"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>40.45099999999999</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>45.9864</v>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr"/>
+      <c r="H1288" t="inlineStr"/>
+      <c r="I1288" t="inlineStr"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>TATN</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>639</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>607.05</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>690.12</v>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr"/>
+      <c r="H1289" t="inlineStr"/>
+      <c r="I1289" t="inlineStr"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>371</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr"/>
+      <c r="H1290" t="inlineStr"/>
+      <c r="I1290" t="inlineStr"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>0.4114950000000001</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>0.372305</v>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr"/>
+      <c r="H1291" t="inlineStr"/>
+      <c r="I1291" t="inlineStr"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>5532</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>5808.6</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>5255.4</v>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr"/>
+      <c r="H1292" t="inlineStr"/>
+      <c r="I1292" t="inlineStr"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>5478</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>5751.900000000001</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>5204.099999999999</v>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr"/>
+      <c r="H1293" t="inlineStr"/>
+      <c r="I1293" t="inlineStr"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>34.881</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>31.559</v>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr"/>
+      <c r="H1294" t="inlineStr"/>
+      <c r="I1294" t="inlineStr"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>ENPG</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>334.845</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>302.955</v>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr"/>
+      <c r="H1295" t="inlineStr"/>
+      <c r="I1295" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1295"/>
+  <dimension ref="A1:I1300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42730,9 +42730,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1282" t="inlineStr"/>
-      <c r="H1282" t="inlineStr"/>
-      <c r="I1282" t="inlineStr"/>
+      <c r="G1282" s="1" t="n">
+        <v>46281.65458432111</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>5264.9</v>
+      </c>
+      <c r="I1282" t="n">
+        <v>5.000000000000006</v>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" s="1" t="n">
@@ -42785,7 +42791,7 @@
         </is>
       </c>
       <c r="G1284" s="1" t="n">
-        <v>46280.65773967267</v>
+        <v>46280.65773967592</v>
       </c>
       <c r="H1284" t="n">
         <v>5549.25</v>
@@ -43090,6 +43096,141 @@
       <c r="G1295" t="inlineStr"/>
       <c r="H1295" t="inlineStr"/>
       <c r="I1295" t="inlineStr"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>5319</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>5584.95</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>5053.05</v>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr"/>
+      <c r="H1296" t="inlineStr"/>
+      <c r="I1296" t="inlineStr"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>21.705</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>22.79025</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>20.61975</v>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr"/>
+      <c r="H1297" t="inlineStr"/>
+      <c r="I1297" t="inlineStr"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>75.22200000000001</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>68.05799999999999</v>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr"/>
+      <c r="H1298" t="inlineStr"/>
+      <c r="I1298" t="inlineStr"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>209.895</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr"/>
+      <c r="H1299" t="inlineStr"/>
+      <c r="I1299" t="inlineStr"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>MOEX</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>159.7995</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>144.5805</v>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr"/>
+      <c r="H1300" t="inlineStr"/>
+      <c r="I1300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1300"/>
+  <dimension ref="A1:I1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42731,7 +42731,7 @@
         </is>
       </c>
       <c r="G1282" s="1" t="n">
-        <v>46281.65458432111</v>
+        <v>46281.65458431713</v>
       </c>
       <c r="H1282" t="n">
         <v>5264.9</v>
@@ -42763,9 +42763,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1283" t="inlineStr"/>
-      <c r="H1283" t="inlineStr"/>
-      <c r="I1283" t="inlineStr"/>
+      <c r="G1283" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="I1283" t="n">
+        <v>2.592869608576413</v>
+      </c>
     </row>
     <row r="1284">
       <c r="A1284" s="1" t="n">
@@ -42823,9 +42829,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1285" t="inlineStr"/>
-      <c r="H1285" t="inlineStr"/>
-      <c r="I1285" t="inlineStr"/>
+      <c r="G1285" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>83.45</v>
+      </c>
+      <c r="I1285" t="n">
+        <v>1.417601890135857</v>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" s="1" t="n">
@@ -42850,9 +42862,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1286" t="inlineStr"/>
-      <c r="H1286" t="inlineStr"/>
-      <c r="I1286" t="inlineStr"/>
+      <c r="G1286" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="I1286" t="n">
+        <v>1.7970401691332</v>
+      </c>
     </row>
     <row r="1287">
       <c r="A1287" s="1" t="n">
@@ -42877,9 +42895,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1287" t="inlineStr"/>
-      <c r="H1287" t="inlineStr"/>
-      <c r="I1287" t="inlineStr"/>
+      <c r="G1287" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>49.7705</v>
+      </c>
+      <c r="I1287" t="n">
+        <v>-5.000000000000004</v>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" s="1" t="n">
@@ -42958,9 +42982,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1290" t="inlineStr"/>
-      <c r="H1290" t="inlineStr"/>
-      <c r="I1290" t="inlineStr"/>
+      <c r="G1290" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="I1290" t="n">
+        <v>-5.000000000000003</v>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" s="1" t="n">
@@ -42985,9 +43015,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1291" t="inlineStr"/>
-      <c r="H1291" t="inlineStr"/>
-      <c r="I1291" t="inlineStr"/>
+      <c r="G1291" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>0.372305</v>
+      </c>
+      <c r="I1291" t="n">
+        <v>5.000000000000007</v>
+      </c>
     </row>
     <row r="1292">
       <c r="A1292" s="1" t="n">
@@ -43012,9 +43048,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1292" t="inlineStr"/>
-      <c r="H1292" t="inlineStr"/>
-      <c r="I1292" t="inlineStr"/>
+      <c r="G1292" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>5255.4</v>
+      </c>
+      <c r="I1292" t="n">
+        <v>5.000000000000006</v>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" s="1" t="n">
@@ -43039,9 +43081,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1293" t="inlineStr"/>
-      <c r="H1293" t="inlineStr"/>
-      <c r="I1293" t="inlineStr"/>
+      <c r="G1293" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>5204.099999999999</v>
+      </c>
+      <c r="I1293" t="n">
+        <v>5.00000000000001</v>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" s="1" t="n">
@@ -43093,9 +43141,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1295" t="inlineStr"/>
-      <c r="H1295" t="inlineStr"/>
-      <c r="I1295" t="inlineStr"/>
+      <c r="G1295" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>302.955</v>
+      </c>
+      <c r="I1295" t="n">
+        <v>4.999999999999998</v>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" s="1" t="n">
@@ -43201,9 +43255,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1299" t="inlineStr"/>
-      <c r="H1299" t="inlineStr"/>
-      <c r="I1299" t="inlineStr"/>
+      <c r="G1299" s="1" t="n">
+        <v>46282.653880327</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="I1299" t="n">
+        <v>5.000000000000003</v>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
@@ -43231,6 +43291,141 @@
       <c r="G1300" t="inlineStr"/>
       <c r="H1300" t="inlineStr"/>
       <c r="I1300" t="inlineStr"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>194.4075</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>175.8925</v>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr"/>
+      <c r="H1301" t="inlineStr"/>
+      <c r="I1301" t="inlineStr"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>5304</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>5569.2</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>5038.8</v>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr"/>
+      <c r="H1302" t="inlineStr"/>
+      <c r="I1302" t="inlineStr"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>5320</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>5586</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>5054</v>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr"/>
+      <c r="H1303" t="inlineStr"/>
+      <c r="I1303" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>372.96</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr"/>
+      <c r="H1304" t="inlineStr"/>
+      <c r="I1304" t="inlineStr"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>97.57650000000001</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>88.2835</v>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr"/>
+      <c r="H1305" t="inlineStr"/>
+      <c r="I1305" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1305"/>
+  <dimension ref="A1:I1310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="G1283" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1283" t="n">
         <v>39.07</v>
@@ -42830,7 +42830,7 @@
         </is>
       </c>
       <c r="G1285" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1285" t="n">
         <v>83.45</v>
@@ -42863,7 +42863,7 @@
         </is>
       </c>
       <c r="G1286" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1286" t="n">
         <v>0.3716</v>
@@ -42896,7 +42896,7 @@
         </is>
       </c>
       <c r="G1287" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1287" t="n">
         <v>49.7705</v>
@@ -42928,9 +42928,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1288" t="inlineStr"/>
-      <c r="H1288" t="inlineStr"/>
-      <c r="I1288" t="inlineStr"/>
+      <c r="G1288" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="I1288" t="n">
+        <v>-4.814466885861901</v>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" s="1" t="n">
@@ -42955,9 +42961,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1289" t="inlineStr"/>
-      <c r="H1289" t="inlineStr"/>
-      <c r="I1289" t="inlineStr"/>
+      <c r="G1289" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>617.8</v>
+      </c>
+      <c r="I1289" t="n">
+        <v>-3.31768388106417</v>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" s="1" t="n">
@@ -42983,7 +42995,7 @@
         </is>
       </c>
       <c r="G1290" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1290" t="n">
         <v>352.45</v>
@@ -43016,7 +43028,7 @@
         </is>
       </c>
       <c r="G1291" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1291" t="n">
         <v>0.372305</v>
@@ -43049,7 +43061,7 @@
         </is>
       </c>
       <c r="G1292" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1292" t="n">
         <v>5255.4</v>
@@ -43082,7 +43094,7 @@
         </is>
       </c>
       <c r="G1293" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1293" t="n">
         <v>5204.099999999999</v>
@@ -43114,9 +43126,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1294" t="inlineStr"/>
-      <c r="H1294" t="inlineStr"/>
-      <c r="I1294" t="inlineStr"/>
+      <c r="G1294" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I1294" t="n">
+        <v>3.281155930162542</v>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" s="1" t="n">
@@ -43142,7 +43160,7 @@
         </is>
       </c>
       <c r="G1295" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1295" t="n">
         <v>302.955</v>
@@ -43256,7 +43274,7 @@
         </is>
       </c>
       <c r="G1299" s="1" t="n">
-        <v>46282.653880327</v>
+        <v>46282.65388032408</v>
       </c>
       <c r="H1299" t="n">
         <v>189.905</v>
@@ -43315,9 +43333,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1301" t="inlineStr"/>
-      <c r="H1301" t="inlineStr"/>
-      <c r="I1301" t="inlineStr"/>
+      <c r="G1301" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>175.8925</v>
+      </c>
+      <c r="I1301" t="n">
+        <v>4.999999999999996</v>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
@@ -43426,6 +43450,141 @@
       <c r="G1305" t="inlineStr"/>
       <c r="H1305" t="inlineStr"/>
       <c r="I1305" t="inlineStr"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>5155</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>5412.75</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>4897.25</v>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr"/>
+      <c r="H1306" t="inlineStr"/>
+      <c r="I1306" t="inlineStr"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>184.695</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>167.105</v>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr"/>
+      <c r="H1307" t="inlineStr"/>
+      <c r="I1307" t="inlineStr"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>5206.5</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>5466.825</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>4946.175</v>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr"/>
+      <c r="H1308" t="inlineStr"/>
+      <c r="I1308" t="inlineStr"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>20.2125</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>18.2875</v>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr"/>
+      <c r="H1309" t="inlineStr"/>
+      <c r="I1309" t="inlineStr"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>33.684</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>30.476</v>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr"/>
+      <c r="H1310" t="inlineStr"/>
+      <c r="I1310" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1310"/>
+  <dimension ref="A1:I1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42929,7 +42929,7 @@
         </is>
       </c>
       <c r="G1288" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1288" t="n">
         <v>40.53</v>
@@ -42962,7 +42962,7 @@
         </is>
       </c>
       <c r="G1289" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1289" t="n">
         <v>617.8</v>
@@ -43127,7 +43127,7 @@
         </is>
       </c>
       <c r="G1294" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1294" t="n">
         <v>32.13</v>
@@ -43192,9 +43192,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1296" t="inlineStr"/>
-      <c r="H1296" t="inlineStr"/>
-      <c r="I1296" t="inlineStr"/>
+      <c r="G1296" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>5022</v>
+      </c>
+      <c r="I1296" t="n">
+        <v>5.583756345177665</v>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
@@ -43219,9 +43225,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1297" t="inlineStr"/>
-      <c r="H1297" t="inlineStr"/>
-      <c r="I1297" t="inlineStr"/>
+      <c r="G1297" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>21.095</v>
+      </c>
+      <c r="I1297" t="n">
+        <v>2.810412347385393</v>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" s="1" t="n">
@@ -43246,9 +43258,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1298" t="inlineStr"/>
-      <c r="H1298" t="inlineStr"/>
-      <c r="I1298" t="inlineStr"/>
+      <c r="G1298" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I1298" t="n">
+        <v>2.149637074260198</v>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" s="1" t="n">
@@ -43306,9 +43324,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1300" t="inlineStr"/>
-      <c r="H1300" t="inlineStr"/>
-      <c r="I1300" t="inlineStr"/>
+      <c r="G1300" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="I1300" t="n">
+        <v>3.535054865628488</v>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
@@ -43334,7 +43358,7 @@
         </is>
       </c>
       <c r="G1301" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1301" t="n">
         <v>175.8925</v>
@@ -43366,9 +43390,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1302" t="inlineStr"/>
-      <c r="H1302" t="inlineStr"/>
-      <c r="I1302" t="inlineStr"/>
+      <c r="G1302" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>5022</v>
+      </c>
+      <c r="I1302" t="n">
+        <v>5.316742081447964</v>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" s="1" t="n">
@@ -43393,9 +43423,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1303" t="inlineStr"/>
-      <c r="H1303" t="inlineStr"/>
-      <c r="I1303" t="inlineStr"/>
+      <c r="G1303" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>5202</v>
+      </c>
+      <c r="I1303" t="n">
+        <v>2.218045112781955</v>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="1" t="n">
@@ -43420,9 +43456,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1304" t="inlineStr"/>
-      <c r="H1304" t="inlineStr"/>
-      <c r="I1304" t="inlineStr"/>
+      <c r="G1304" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="I1304" t="n">
+        <v>-1.337274774774775</v>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" s="1" t="n">
@@ -43447,9 +43489,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1305" t="inlineStr"/>
-      <c r="H1305" t="inlineStr"/>
-      <c r="I1305" t="inlineStr"/>
+      <c r="G1305" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="I1305" t="n">
+        <v>-4.465726891208427</v>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" s="1" t="n">
@@ -43474,9 +43522,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1306" t="inlineStr"/>
-      <c r="H1306" t="inlineStr"/>
-      <c r="I1306" t="inlineStr"/>
+      <c r="G1306" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>5022</v>
+      </c>
+      <c r="I1306" t="n">
+        <v>2.580019398642095</v>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" s="1" t="n">
@@ -43501,9 +43555,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1307" t="inlineStr"/>
-      <c r="H1307" t="inlineStr"/>
-      <c r="I1307" t="inlineStr"/>
+      <c r="G1307" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="I1307" t="n">
+        <v>1.790790221716888</v>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" s="1" t="n">
@@ -43528,9 +43588,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1308" t="inlineStr"/>
-      <c r="H1308" t="inlineStr"/>
-      <c r="I1308" t="inlineStr"/>
+      <c r="G1308" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>5202</v>
+      </c>
+      <c r="I1308" t="n">
+        <v>0.08643042350907519</v>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" s="1" t="n">
@@ -43555,9 +43621,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1309" t="inlineStr"/>
-      <c r="H1309" t="inlineStr"/>
-      <c r="I1309" t="inlineStr"/>
+      <c r="G1309" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="I1309" t="n">
+        <v>1.090909090909095</v>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" s="1" t="n">
@@ -43582,9 +43654,177 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1310" t="inlineStr"/>
-      <c r="H1310" t="inlineStr"/>
-      <c r="I1310" t="inlineStr"/>
+      <c r="G1310" s="1" t="n">
+        <v>46286.72618742281</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="I1310" t="n">
+        <v>-0.06234413965088256</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>90.72499999999999</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr"/>
+      <c r="H1311" t="inlineStr"/>
+      <c r="I1311" t="inlineStr"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>5093</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>5347.650000000001</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>4838.349999999999</v>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr"/>
+      <c r="H1312" t="inlineStr"/>
+      <c r="I1312" t="inlineStr"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>5201.5</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>5461.575</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>4941.425</v>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr"/>
+      <c r="H1313" t="inlineStr"/>
+      <c r="I1313" t="inlineStr"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>34.0095</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>30.7705</v>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr"/>
+      <c r="H1314" t="inlineStr"/>
+      <c r="I1314" t="inlineStr"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>41.1705</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>37.2495</v>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr"/>
+      <c r="H1315" t="inlineStr"/>
+      <c r="I1315" t="inlineStr"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>40.405</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>42.42525000000001</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>38.38475</v>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr"/>
+      <c r="H1316" t="inlineStr"/>
+      <c r="I1316" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1316"/>
+  <dimension ref="A1:I1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43193,7 +43193,7 @@
         </is>
       </c>
       <c r="G1296" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1296" t="n">
         <v>5022</v>
@@ -43226,7 +43226,7 @@
         </is>
       </c>
       <c r="G1297" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1297" t="n">
         <v>21.095</v>
@@ -43259,7 +43259,7 @@
         </is>
       </c>
       <c r="G1298" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1298" t="n">
         <v>70.09999999999999</v>
@@ -43325,7 +43325,7 @@
         </is>
       </c>
       <c r="G1300" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1300" t="n">
         <v>146.81</v>
@@ -43391,7 +43391,7 @@
         </is>
       </c>
       <c r="G1302" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1302" t="n">
         <v>5022</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="G1303" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1303" t="n">
         <v>5202</v>
@@ -43457,7 +43457,7 @@
         </is>
       </c>
       <c r="G1304" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1304" t="n">
         <v>359.95</v>
@@ -43490,7 +43490,7 @@
         </is>
       </c>
       <c r="G1305" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1305" t="n">
         <v>97.08</v>
@@ -43523,7 +43523,7 @@
         </is>
       </c>
       <c r="G1306" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1306" t="n">
         <v>5022</v>
@@ -43556,7 +43556,7 @@
         </is>
       </c>
       <c r="G1307" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1307" t="n">
         <v>172.75</v>
@@ -43589,7 +43589,7 @@
         </is>
       </c>
       <c r="G1308" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1308" t="n">
         <v>5202</v>
@@ -43622,7 +43622,7 @@
         </is>
       </c>
       <c r="G1309" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1309" t="n">
         <v>19.04</v>
@@ -43655,7 +43655,7 @@
         </is>
       </c>
       <c r="G1310" s="1" t="n">
-        <v>46286.72618742281</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1310" t="n">
         <v>32.1</v>
@@ -43825,6 +43825,141 @@
       <c r="G1316" t="inlineStr"/>
       <c r="H1316" t="inlineStr"/>
       <c r="I1316" t="inlineStr"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>5043</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>5295.150000000001</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>4790.849999999999</v>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr"/>
+      <c r="H1317" t="inlineStr"/>
+      <c r="I1317" t="inlineStr"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>5207</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>5467.35</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>4946.65</v>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr"/>
+      <c r="H1318" t="inlineStr"/>
+      <c r="I1318" t="inlineStr"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>41.1285</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>37.2115</v>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr"/>
+      <c r="H1319" t="inlineStr"/>
+      <c r="I1319" t="inlineStr"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>88.515</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>80.08499999999999</v>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr"/>
+      <c r="H1320" t="inlineStr"/>
+      <c r="I1320" t="inlineStr"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>102.2805</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>92.53949999999999</v>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr"/>
+      <c r="H1321" t="inlineStr"/>
+      <c r="I1321" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1321"/>
+  <dimension ref="A1:I1329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43687,9 +43687,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1311" t="inlineStr"/>
-      <c r="H1311" t="inlineStr"/>
-      <c r="I1311" t="inlineStr"/>
+      <c r="G1311" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="I1311" t="n">
+        <v>6.052356020942409</v>
+      </c>
     </row>
     <row r="1312">
       <c r="A1312" s="1" t="n">
@@ -43714,9 +43720,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1312" t="inlineStr"/>
-      <c r="H1312" t="inlineStr"/>
-      <c r="I1312" t="inlineStr"/>
+      <c r="G1312" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>5030</v>
+      </c>
+      <c r="I1312" t="n">
+        <v>1.23699194973493</v>
+      </c>
     </row>
     <row r="1313">
       <c r="A1313" s="1" t="n">
@@ -43741,9 +43753,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1313" t="inlineStr"/>
-      <c r="H1313" t="inlineStr"/>
-      <c r="I1313" t="inlineStr"/>
+      <c r="G1313" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>5392</v>
+      </c>
+      <c r="I1313" t="n">
+        <v>-3.662405075459002</v>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" s="1" t="n">
@@ -43768,9 +43786,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1314" t="inlineStr"/>
-      <c r="H1314" t="inlineStr"/>
-      <c r="I1314" t="inlineStr"/>
+      <c r="G1314" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I1314" t="n">
+        <v>-1.265822784810116</v>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" s="1" t="n">
@@ -43795,9 +43819,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1315" t="inlineStr"/>
-      <c r="H1315" t="inlineStr"/>
-      <c r="I1315" t="inlineStr"/>
+      <c r="G1315" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I1315" t="n">
+        <v>0.1275184901810871</v>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" s="1" t="n">
@@ -43822,9 +43852,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1316" t="inlineStr"/>
-      <c r="H1316" t="inlineStr"/>
-      <c r="I1316" t="inlineStr"/>
+      <c r="G1316" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>40.395</v>
+      </c>
+      <c r="I1316" t="n">
+        <v>0.02474941220145529</v>
+      </c>
     </row>
     <row r="1317">
       <c r="A1317" s="1" t="n">
@@ -43957,9 +43993,231 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1321" t="inlineStr"/>
-      <c r="H1321" t="inlineStr"/>
-      <c r="I1321" t="inlineStr"/>
+      <c r="G1321" s="1" t="n">
+        <v>46289.65978609028</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>102.2805</v>
+      </c>
+      <c r="I1321" t="n">
+        <v>-5.000000000000007</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>0.363375</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr"/>
+      <c r="H1322" t="inlineStr"/>
+      <c r="I1322" t="inlineStr"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>347.3674999999999</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>394.902</v>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr"/>
+      <c r="H1323" t="inlineStr"/>
+      <c r="I1323" t="inlineStr"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>97.565</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>110.916</v>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr"/>
+      <c r="H1324" t="inlineStr"/>
+      <c r="I1324" t="inlineStr"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>2955</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>3102.75</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>2807.25</v>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr"/>
+      <c r="H1325" t="inlineStr"/>
+      <c r="I1325" t="inlineStr"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>23.3205</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr"/>
+      <c r="H1326" t="inlineStr"/>
+      <c r="I1326" t="inlineStr"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>20.979</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>18.981</v>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr"/>
+      <c r="H1327" t="inlineStr"/>
+      <c r="I1327" t="inlineStr"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>CHMF</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>658.2</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>691.1100000000001</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>625.29</v>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr"/>
+      <c r="H1328" t="inlineStr"/>
+      <c r="I1328" t="inlineStr"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>7.8645</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>7.1155</v>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr"/>
+      <c r="H1329" t="inlineStr"/>
+      <c r="I1329" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1329"/>
+  <dimension ref="A1:I1335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43688,7 +43688,7 @@
         </is>
       </c>
       <c r="G1311" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1311" t="n">
         <v>101.28</v>
@@ -43721,7 +43721,7 @@
         </is>
       </c>
       <c r="G1312" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1312" t="n">
         <v>5030</v>
@@ -43754,7 +43754,7 @@
         </is>
       </c>
       <c r="G1313" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1313" t="n">
         <v>5392</v>
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="G1314" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1314" t="n">
         <v>32.8</v>
@@ -43820,7 +43820,7 @@
         </is>
       </c>
       <c r="G1315" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1315" t="n">
         <v>39.16</v>
@@ -43853,7 +43853,7 @@
         </is>
       </c>
       <c r="G1316" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1316" t="n">
         <v>40.395</v>
@@ -43885,9 +43885,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1317" t="inlineStr"/>
-      <c r="H1317" t="inlineStr"/>
-      <c r="I1317" t="inlineStr"/>
+      <c r="G1317" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>5115</v>
+      </c>
+      <c r="I1317" t="n">
+        <v>-1.427721594289113</v>
+      </c>
     </row>
     <row r="1318">
       <c r="A1318" s="1" t="n">
@@ -43912,9 +43918,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1318" t="inlineStr"/>
-      <c r="H1318" t="inlineStr"/>
-      <c r="I1318" t="inlineStr"/>
+      <c r="G1318" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>5376.5</v>
+      </c>
+      <c r="I1318" t="n">
+        <v>-3.255233339734972</v>
+      </c>
     </row>
     <row r="1319">
       <c r="A1319" s="1" t="n">
@@ -43939,9 +43951,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1319" t="inlineStr"/>
-      <c r="H1319" t="inlineStr"/>
-      <c r="I1319" t="inlineStr"/>
+      <c r="G1319" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="I1319" t="n">
+        <v>0.2552974214960465</v>
+      </c>
     </row>
     <row r="1320">
       <c r="A1320" s="1" t="n">
@@ -43966,9 +43984,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1320" t="inlineStr"/>
-      <c r="H1320" t="inlineStr"/>
-      <c r="I1320" t="inlineStr"/>
+      <c r="G1320" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="I1320" t="n">
+        <v>-0.6524317912218235</v>
+      </c>
     </row>
     <row r="1321">
       <c r="A1321" s="1" t="n">
@@ -43994,7 +44018,7 @@
         </is>
       </c>
       <c r="G1321" s="1" t="n">
-        <v>46289.65978609028</v>
+        <v>46289.65978608796</v>
       </c>
       <c r="H1321" t="n">
         <v>102.2805</v>
@@ -44134,9 +44158,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1326" t="inlineStr"/>
-      <c r="H1326" t="inlineStr"/>
-      <c r="I1326" t="inlineStr"/>
+      <c r="G1326" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="I1326" t="n">
+        <v>5.000000000000008</v>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" s="1" t="n">
@@ -44215,9 +44245,177 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1329" t="inlineStr"/>
-      <c r="H1329" t="inlineStr"/>
-      <c r="I1329" t="inlineStr"/>
+      <c r="G1329" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>7.1155</v>
+      </c>
+      <c r="I1329" t="n">
+        <v>5.000000000000004</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>2997.5</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>2847.625</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>3237.3</v>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr"/>
+      <c r="H1330" t="inlineStr"/>
+      <c r="I1330" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>125.685</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>113.715</v>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr"/>
+      <c r="H1331" t="inlineStr"/>
+      <c r="I1331" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>24.8115</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>22.4485</v>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr"/>
+      <c r="H1332" t="inlineStr"/>
+      <c r="I1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>5075</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>5328.75</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>4821.25</v>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr"/>
+      <c r="H1333" t="inlineStr"/>
+      <c r="I1333" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>5410</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>5680.5</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>5139.5</v>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr"/>
+      <c r="H1334" t="inlineStr"/>
+      <c r="I1334" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>22.6275</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>20.4725</v>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr"/>
+      <c r="H1335" t="inlineStr"/>
+      <c r="I1335" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1335"/>
+  <dimension ref="A1:I1340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43886,7 +43886,7 @@
         </is>
       </c>
       <c r="G1317" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1317" t="n">
         <v>5115</v>
@@ -43919,7 +43919,7 @@
         </is>
       </c>
       <c r="G1318" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1318" t="n">
         <v>5376.5</v>
@@ -43952,7 +43952,7 @@
         </is>
       </c>
       <c r="G1319" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1319" t="n">
         <v>39.07</v>
@@ -43985,7 +43985,7 @@
         </is>
       </c>
       <c r="G1320" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1320" t="n">
         <v>84.84999999999999</v>
@@ -44050,9 +44050,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1322" t="inlineStr"/>
-      <c r="H1322" t="inlineStr"/>
-      <c r="I1322" t="inlineStr"/>
+      <c r="G1322" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="I1322" t="n">
+        <v>-0.9411764705882332</v>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" s="1" t="n">
@@ -44077,9 +44083,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1323" t="inlineStr"/>
-      <c r="H1323" t="inlineStr"/>
-      <c r="I1323" t="inlineStr"/>
+      <c r="G1323" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>356.4</v>
+      </c>
+      <c r="I1323" t="n">
+        <v>-2.529741556132914</v>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" s="1" t="n">
@@ -44104,9 +44116,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1324" t="inlineStr"/>
-      <c r="H1324" t="inlineStr"/>
-      <c r="I1324" t="inlineStr"/>
+      <c r="G1324" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="I1324" t="n">
+        <v>-4.294060370009733</v>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" s="1" t="n">
@@ -44131,9 +44149,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1325" t="inlineStr"/>
-      <c r="H1325" t="inlineStr"/>
-      <c r="I1325" t="inlineStr"/>
+      <c r="G1325" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>2921.5</v>
+      </c>
+      <c r="I1325" t="n">
+        <v>1.133671742808799</v>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" s="1" t="n">
@@ -44159,7 +44183,7 @@
         </is>
       </c>
       <c r="G1326" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1326" t="n">
         <v>21.0995</v>
@@ -44191,9 +44215,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1327" t="inlineStr"/>
-      <c r="H1327" t="inlineStr"/>
-      <c r="I1327" t="inlineStr"/>
+      <c r="G1327" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="I1327" t="n">
+        <v>3.653653653653656</v>
+      </c>
     </row>
     <row r="1328">
       <c r="A1328" s="1" t="n">
@@ -44218,9 +44248,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1328" t="inlineStr"/>
-      <c r="H1328" t="inlineStr"/>
-      <c r="I1328" t="inlineStr"/>
+      <c r="G1328" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>627</v>
+      </c>
+      <c r="I1328" t="n">
+        <v>4.740200546946224</v>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" s="1" t="n">
@@ -44246,7 +44282,7 @@
         </is>
       </c>
       <c r="G1329" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1329" t="n">
         <v>7.1155</v>
@@ -44278,9 +44314,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1330" t="inlineStr"/>
-      <c r="H1330" t="inlineStr"/>
-      <c r="I1330" t="inlineStr"/>
+      <c r="G1330" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>2921.5</v>
+      </c>
+      <c r="I1330" t="n">
+        <v>-2.535446205170976</v>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" s="1" t="n">
@@ -44305,9 +44347,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1331" t="inlineStr"/>
-      <c r="H1331" t="inlineStr"/>
-      <c r="I1331" t="inlineStr"/>
+      <c r="G1331" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="I1331" t="n">
+        <v>2.205513784461153</v>
+      </c>
     </row>
     <row r="1332">
       <c r="A1332" s="1" t="n">
@@ -44332,9 +44380,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1332" t="inlineStr"/>
-      <c r="H1332" t="inlineStr"/>
-      <c r="I1332" t="inlineStr"/>
+      <c r="G1332" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="I1332" t="n">
+        <v>1.777401608125257</v>
+      </c>
     </row>
     <row r="1333">
       <c r="A1333" s="1" t="n">
@@ -44359,9 +44413,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1333" t="inlineStr"/>
-      <c r="H1333" t="inlineStr"/>
-      <c r="I1333" t="inlineStr"/>
+      <c r="G1333" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>5035</v>
+      </c>
+      <c r="I1333" t="n">
+        <v>0.7881773399014778</v>
+      </c>
     </row>
     <row r="1334">
       <c r="A1334" s="1" t="n">
@@ -44386,9 +44446,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1334" t="inlineStr"/>
-      <c r="H1334" t="inlineStr"/>
-      <c r="I1334" t="inlineStr"/>
+      <c r="G1334" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>5306</v>
+      </c>
+      <c r="I1334" t="n">
+        <v>1.922365988909427</v>
+      </c>
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
@@ -44413,9 +44479,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1335" t="inlineStr"/>
-      <c r="H1335" t="inlineStr"/>
-      <c r="I1335" t="inlineStr"/>
+      <c r="G1335" s="1" t="n">
+        <v>46293.78092691197</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>20.355</v>
+      </c>
+      <c r="I1335" t="n">
+        <v>5.54524361948956</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>5073</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>5326.650000000001</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>4819.349999999999</v>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr"/>
+      <c r="H1336" t="inlineStr"/>
+      <c r="I1336" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>5385</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>5654.25</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>5115.75</v>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr"/>
+      <c r="H1337" t="inlineStr"/>
+      <c r="I1337" t="inlineStr"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>7.161</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>7.51905</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>6.802949999999999</v>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr"/>
+      <c r="H1338" t="inlineStr"/>
+      <c r="I1338" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>72.57600000000001</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>65.664</v>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr"/>
+      <c r="H1339" t="inlineStr"/>
+      <c r="I1339" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>20.4435</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>18.4965</v>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr"/>
+      <c r="H1340" t="inlineStr"/>
+      <c r="I1340" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1340"/>
+  <dimension ref="A1:I1346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44051,7 +44051,7 @@
         </is>
       </c>
       <c r="G1322" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1322" t="n">
         <v>0.3789</v>
@@ -44084,7 +44084,7 @@
         </is>
       </c>
       <c r="G1323" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1323" t="n">
         <v>356.4</v>
@@ -44117,7 +44117,7 @@
         </is>
       </c>
       <c r="G1324" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1324" t="n">
         <v>98.29000000000001</v>
@@ -44150,7 +44150,7 @@
         </is>
       </c>
       <c r="G1325" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1325" t="n">
         <v>2921.5</v>
@@ -44216,7 +44216,7 @@
         </is>
       </c>
       <c r="G1327" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1327" t="n">
         <v>19.25</v>
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="G1328" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1328" t="n">
         <v>627</v>
@@ -44315,7 +44315,7 @@
         </is>
       </c>
       <c r="G1330" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1330" t="n">
         <v>2921.5</v>
@@ -44348,7 +44348,7 @@
         </is>
       </c>
       <c r="G1331" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1331" t="n">
         <v>117.06</v>
@@ -44381,7 +44381,7 @@
         </is>
       </c>
       <c r="G1332" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1332" t="n">
         <v>23.21</v>
@@ -44414,7 +44414,7 @@
         </is>
       </c>
       <c r="G1333" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1333" t="n">
         <v>5035</v>
@@ -44447,7 +44447,7 @@
         </is>
       </c>
       <c r="G1334" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1334" t="n">
         <v>5306</v>
@@ -44480,7 +44480,7 @@
         </is>
       </c>
       <c r="G1335" s="1" t="n">
-        <v>46293.78092691197</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1335" t="n">
         <v>20.355</v>
@@ -44620,9 +44620,177 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1340" t="inlineStr"/>
-      <c r="H1340" t="inlineStr"/>
-      <c r="I1340" t="inlineStr"/>
+      <c r="G1340" s="1" t="n">
+        <v>46294.71719436274</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>18.4965</v>
+      </c>
+      <c r="I1340" t="n">
+        <v>4.999999999999989</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>555.95</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>528.1525</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>600.426</v>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr"/>
+      <c r="H1341" t="inlineStr"/>
+      <c r="I1341" t="inlineStr"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>0.3924900000000001</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr"/>
+      <c r="H1342" t="inlineStr"/>
+      <c r="I1342" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>5043</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>5295.150000000001</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>4790.849999999999</v>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr"/>
+      <c r="H1343" t="inlineStr"/>
+      <c r="I1343" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>5311.5</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>5577.075</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>5045.925</v>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr"/>
+      <c r="H1344" t="inlineStr"/>
+      <c r="I1344" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>20.285</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>21.29925</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>19.27075</v>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr"/>
+      <c r="H1345" t="inlineStr"/>
+      <c r="I1345" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>19.8765</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>17.9835</v>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr"/>
+      <c r="H1346" t="inlineStr"/>
+      <c r="I1346" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1346"/>
+  <dimension ref="A1:I1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44621,7 +44621,7 @@
         </is>
       </c>
       <c r="G1340" s="1" t="n">
-        <v>46294.71719436274</v>
+        <v>46294.71719436342</v>
       </c>
       <c r="H1340" t="n">
         <v>18.4965</v>
@@ -44791,6 +44791,141 @@
       <c r="G1346" t="inlineStr"/>
       <c r="H1346" t="inlineStr"/>
       <c r="I1346" t="inlineStr"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>5010</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>5260.5</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>4759.5</v>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr"/>
+      <c r="H1347" t="inlineStr"/>
+      <c r="I1347" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>23.505</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>24.68025</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>22.32975</v>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="inlineStr"/>
+      <c r="I1348" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>19.4985</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>17.6415</v>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="inlineStr"/>
+      <c r="I1349" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>72.13500000000001</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>65.265</v>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr"/>
+      <c r="H1350" t="inlineStr"/>
+      <c r="I1350" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>20.485</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>21.50925</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>19.46075</v>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="inlineStr"/>
+      <c r="I1351" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1351"/>
+  <dimension ref="A1:I1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44539,9 +44539,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1337" t="inlineStr"/>
-      <c r="H1337" t="inlineStr"/>
-      <c r="I1337" t="inlineStr"/>
+      <c r="G1337" s="1" t="n">
+        <v>46296.73625504094</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>5416</v>
+      </c>
+      <c r="I1337" t="n">
+        <v>-0.5756731662024142</v>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" s="1" t="n">
@@ -44566,9 +44572,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1338" t="inlineStr"/>
-      <c r="H1338" t="inlineStr"/>
-      <c r="I1338" t="inlineStr"/>
+      <c r="G1338" s="1" t="n">
+        <v>46296.73625504094</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>6.925</v>
+      </c>
+      <c r="I1338" t="n">
+        <v>3.295629102080712</v>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="1" t="n">
@@ -44593,9 +44605,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1339" t="inlineStr"/>
-      <c r="H1339" t="inlineStr"/>
-      <c r="I1339" t="inlineStr"/>
+      <c r="G1339" s="1" t="n">
+        <v>46296.73625504094</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="I1339" t="n">
+        <v>1.562499999999997</v>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" s="1" t="n">
@@ -44926,6 +44944,141 @@
       <c r="G1351" t="inlineStr"/>
       <c r="H1351" t="inlineStr"/>
       <c r="I1351" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>7.23975</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>6.550249999999999</v>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="inlineStr"/>
+      <c r="I1352" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>39.965</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>41.96325</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>37.96675</v>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="inlineStr"/>
+      <c r="I1353" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>60.90000000000001</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>55.09999999999999</v>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr"/>
+      <c r="H1354" t="inlineStr"/>
+      <c r="I1354" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>40.44600000000001</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>36.594</v>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="inlineStr"/>
+      <c r="I1355" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>15.792</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>14.288</v>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="inlineStr"/>
+      <c r="I1356" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -44540,7 +44540,7 @@
         </is>
       </c>
       <c r="G1337" s="1" t="n">
-        <v>46296.73625504094</v>
+        <v>46296.73625504629</v>
       </c>
       <c r="H1337" t="n">
         <v>5416</v>
@@ -44573,7 +44573,7 @@
         </is>
       </c>
       <c r="G1338" s="1" t="n">
-        <v>46296.73625504094</v>
+        <v>46296.73625504629</v>
       </c>
       <c r="H1338" t="n">
         <v>6.925</v>
@@ -44606,7 +44606,7 @@
         </is>
       </c>
       <c r="G1339" s="1" t="n">
-        <v>46296.73625504094</v>
+        <v>46296.73625504629</v>
       </c>
       <c r="H1339" t="n">
         <v>68.04000000000001</v>
@@ -44671,9 +44671,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1341" t="inlineStr"/>
-      <c r="H1341" t="inlineStr"/>
-      <c r="I1341" t="inlineStr"/>
+      <c r="G1341" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>556.55</v>
+      </c>
+      <c r="I1341" t="n">
+        <v>0.1079233744041567</v>
+      </c>
     </row>
     <row r="1342">
       <c r="A1342" s="1" t="n">
@@ -44698,9 +44704,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1342" t="inlineStr"/>
-      <c r="H1342" t="inlineStr"/>
-      <c r="I1342" t="inlineStr"/>
+      <c r="G1342" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="I1342" t="n">
+        <v>-1.444622792937389</v>
+      </c>
     </row>
     <row r="1343">
       <c r="A1343" s="1" t="n">
@@ -44752,9 +44764,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1344" t="inlineStr"/>
-      <c r="H1344" t="inlineStr"/>
-      <c r="I1344" t="inlineStr"/>
+      <c r="G1344" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>5416</v>
+      </c>
+      <c r="I1344" t="n">
+        <v>-1.96742916313659</v>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" s="1" t="n">
@@ -44779,9 +44797,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1345" t="inlineStr"/>
-      <c r="H1345" t="inlineStr"/>
-      <c r="I1345" t="inlineStr"/>
+      <c r="G1345" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="I1345" t="n">
+        <v>-0.3204338180921926</v>
+      </c>
     </row>
     <row r="1346">
       <c r="A1346" s="1" t="n">
@@ -44806,9 +44830,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1346" t="inlineStr"/>
-      <c r="H1346" t="inlineStr"/>
-      <c r="I1346" t="inlineStr"/>
+      <c r="G1346" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="I1346" t="n">
+        <v>2.482831484416264</v>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" s="1" t="n">

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1356"/>
+  <dimension ref="A1:I1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44512,9 +44512,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1336" t="inlineStr"/>
-      <c r="H1336" t="inlineStr"/>
-      <c r="I1336" t="inlineStr"/>
+      <c r="G1336" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>5221</v>
+      </c>
+      <c r="I1336" t="n">
+        <v>-2.917405874236152</v>
+      </c>
     </row>
     <row r="1337">
       <c r="A1337" s="1" t="n">
@@ -44672,7 +44678,7 @@
         </is>
       </c>
       <c r="G1341" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1341" t="n">
         <v>556.55</v>
@@ -44705,7 +44711,7 @@
         </is>
       </c>
       <c r="G1342" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1342" t="n">
         <v>0.3792</v>
@@ -44737,9 +44743,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1343" t="inlineStr"/>
-      <c r="H1343" t="inlineStr"/>
-      <c r="I1343" t="inlineStr"/>
+      <c r="G1343" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>5221</v>
+      </c>
+      <c r="I1343" t="n">
+        <v>-3.529645052548087</v>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" s="1" t="n">
@@ -44765,7 +44777,7 @@
         </is>
       </c>
       <c r="G1344" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1344" t="n">
         <v>5416</v>
@@ -44798,7 +44810,7 @@
         </is>
       </c>
       <c r="G1345" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1345" t="n">
         <v>20.35</v>
@@ -44831,7 +44843,7 @@
         </is>
       </c>
       <c r="G1346" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1346" t="n">
         <v>18.46</v>
@@ -44863,9 +44875,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1347" t="inlineStr"/>
-      <c r="H1347" t="inlineStr"/>
-      <c r="I1347" t="inlineStr"/>
+      <c r="G1347" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>5221</v>
+      </c>
+      <c r="I1347" t="n">
+        <v>-4.211576846307386</v>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" s="1" t="n">
@@ -44890,9 +44908,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1348" t="inlineStr"/>
-      <c r="H1348" t="inlineStr"/>
-      <c r="I1348" t="inlineStr"/>
+      <c r="G1348" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="I1348" t="n">
+        <v>-1.340140395660503</v>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" s="1" t="n">
@@ -44917,9 +44941,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1349" t="inlineStr"/>
-      <c r="H1349" t="inlineStr"/>
-      <c r="I1349" t="inlineStr"/>
+      <c r="G1349" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="I1349" t="n">
+        <v>-4.577275175013471</v>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" s="1" t="n">
@@ -44944,9 +44974,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1350" t="inlineStr"/>
-      <c r="H1350" t="inlineStr"/>
-      <c r="I1350" t="inlineStr"/>
+      <c r="G1350" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="I1350" t="n">
+        <v>-6.055312954876269</v>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" s="1" t="n">
@@ -44971,9 +45007,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1351" t="inlineStr"/>
-      <c r="H1351" t="inlineStr"/>
-      <c r="I1351" t="inlineStr"/>
+      <c r="G1351" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>21.855</v>
+      </c>
+      <c r="I1351" t="n">
+        <v>-6.687820356358317</v>
+      </c>
     </row>
     <row r="1352">
       <c r="A1352" s="1" t="n">
@@ -44998,9 +45040,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1352" t="inlineStr"/>
-      <c r="H1352" t="inlineStr"/>
-      <c r="I1352" t="inlineStr"/>
+      <c r="G1352" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>7.034</v>
+      </c>
+      <c r="I1352" t="n">
+        <v>-2.015953589557654</v>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" s="1" t="n">
@@ -45025,9 +45073,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1353" t="inlineStr"/>
-      <c r="H1353" t="inlineStr"/>
-      <c r="I1353" t="inlineStr"/>
+      <c r="G1353" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>41.915</v>
+      </c>
+      <c r="I1353" t="n">
+        <v>-4.879269360690594</v>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" s="1" t="n">
@@ -45052,9 +45106,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1354" t="inlineStr"/>
-      <c r="H1354" t="inlineStr"/>
-      <c r="I1354" t="inlineStr"/>
+      <c r="G1354" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="I1354" t="n">
+        <v>-2.379310344827591</v>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" s="1" t="n">
@@ -45079,9 +45139,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1355" t="inlineStr"/>
-      <c r="H1355" t="inlineStr"/>
-      <c r="I1355" t="inlineStr"/>
+      <c r="G1355" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I1355" t="n">
+        <v>-3.322949117341625</v>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" s="1" t="n">
@@ -45106,9 +45172,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1356" t="inlineStr"/>
-      <c r="H1356" t="inlineStr"/>
-      <c r="I1356" t="inlineStr"/>
+      <c r="G1356" s="1" t="n">
+        <v>46300.80343163587</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>15.595</v>
+      </c>
+      <c r="I1356" t="n">
+        <v>-3.690159574468095</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>5070</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>5323.5</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>4816.5</v>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="inlineStr"/>
+      <c r="I1357" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>5428</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>5699.400000000001</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>5156.599999999999</v>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="inlineStr"/>
+      <c r="I1358" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>20.945</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>21.99225</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>19.89775</v>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="inlineStr"/>
+      <c r="I1359" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>19.845</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>17.955</v>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr"/>
+      <c r="I1360" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>41.2965</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>37.36349999999999</v>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="inlineStr"/>
+      <c r="I1361" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1361"/>
+  <dimension ref="A1:I1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44513,7 +44513,7 @@
         </is>
       </c>
       <c r="G1336" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1336" t="n">
         <v>5221</v>
@@ -44744,7 +44744,7 @@
         </is>
       </c>
       <c r="G1343" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1343" t="n">
         <v>5221</v>
@@ -44876,7 +44876,7 @@
         </is>
       </c>
       <c r="G1347" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1347" t="n">
         <v>5221</v>
@@ -44909,7 +44909,7 @@
         </is>
       </c>
       <c r="G1348" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1348" t="n">
         <v>23.82</v>
@@ -44942,7 +44942,7 @@
         </is>
       </c>
       <c r="G1349" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1349" t="n">
         <v>19.42</v>
@@ -44975,7 +44975,7 @@
         </is>
       </c>
       <c r="G1350" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1350" t="n">
         <v>72.86</v>
@@ -45008,7 +45008,7 @@
         </is>
       </c>
       <c r="G1351" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1351" t="n">
         <v>21.855</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="G1352" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1352" t="n">
         <v>7.034</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="G1353" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1353" t="n">
         <v>41.915</v>
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="G1354" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1354" t="n">
         <v>59.38</v>
@@ -45140,7 +45140,7 @@
         </is>
       </c>
       <c r="G1355" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1355" t="n">
         <v>39.8</v>
@@ -45173,7 +45173,7 @@
         </is>
       </c>
       <c r="G1356" s="1" t="n">
-        <v>46300.80343163587</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1356" t="n">
         <v>15.595</v>
@@ -45259,9 +45259,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1359" t="inlineStr"/>
-      <c r="H1359" t="inlineStr"/>
-      <c r="I1359" t="inlineStr"/>
+      <c r="G1359" s="1" t="n">
+        <v>46301.7230736009</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>21.99225</v>
+      </c>
+      <c r="I1359" t="n">
+        <v>-4.999999999999991</v>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" s="1" t="n">
@@ -45316,6 +45322,222 @@
       <c r="G1361" t="inlineStr"/>
       <c r="H1361" t="inlineStr"/>
       <c r="I1361" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>573.6</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>544.92</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>619.4880000000001</v>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr"/>
+      <c r="I1362" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>0.416448</v>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="inlineStr"/>
+      <c r="I1363" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>VTBR</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>54.305</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>51.58975</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>58.64940000000001</v>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr"/>
+      <c r="I1364" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>32.10999999999999</v>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr"/>
+      <c r="I1365" t="inlineStr"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>20.265</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>18.335</v>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr"/>
+      <c r="I1366" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>7.057</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>7.40985</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>6.70415</v>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr"/>
+      <c r="I1367" t="inlineStr"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>102.333</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>92.58699999999999</v>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr"/>
+      <c r="I1368" t="inlineStr"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>119.36</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>125.328</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>113.392</v>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr"/>
+      <c r="I1369" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1369"/>
+  <dimension ref="A1:I1374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45260,7 +45260,7 @@
         </is>
       </c>
       <c r="G1359" s="1" t="n">
-        <v>46301.7230736009</v>
+        <v>46301.72307359954</v>
       </c>
       <c r="H1359" t="n">
         <v>21.99225</v>
@@ -45538,6 +45538,141 @@
       <c r="G1369" t="inlineStr"/>
       <c r="H1369" t="inlineStr"/>
       <c r="I1369" t="inlineStr"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>5587.5</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>5866.875</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>5308.125</v>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="inlineStr"/>
+      <c r="I1370" t="inlineStr"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>5210</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>5470.5</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>4949.5</v>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr"/>
+      <c r="H1371" t="inlineStr"/>
+      <c r="I1371" t="inlineStr"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>VTBR</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>58.422</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>52.858</v>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr"/>
+      <c r="H1372" t="inlineStr"/>
+      <c r="I1372" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>63</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="inlineStr"/>
+      <c r="I1373" t="inlineStr"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>42.21000000000001</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="inlineStr"/>
+      <c r="I1374" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1374"/>
+  <dimension ref="A1:I1379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45205,9 +45205,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1357" t="inlineStr"/>
-      <c r="H1357" t="inlineStr"/>
-      <c r="I1357" t="inlineStr"/>
+      <c r="G1357" s="1" t="n">
+        <v>46303.74037910163</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>5203</v>
+      </c>
+      <c r="I1357" t="n">
+        <v>-2.6232741617357</v>
+      </c>
     </row>
     <row r="1358">
       <c r="A1358" s="1" t="n">
@@ -45232,9 +45238,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1358" t="inlineStr"/>
-      <c r="H1358" t="inlineStr"/>
-      <c r="I1358" t="inlineStr"/>
+      <c r="G1358" s="1" t="n">
+        <v>46303.74037910163</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>5582.5</v>
+      </c>
+      <c r="I1358" t="n">
+        <v>-2.846352247605011</v>
+      </c>
     </row>
     <row r="1359">
       <c r="A1359" s="1" t="n">
@@ -45292,9 +45304,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1360" t="inlineStr"/>
-      <c r="H1360" t="inlineStr"/>
-      <c r="I1360" t="inlineStr"/>
+      <c r="G1360" s="1" t="n">
+        <v>46303.74037910163</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="I1360" t="n">
+        <v>-0.9523809523809509</v>
+      </c>
     </row>
     <row r="1361">
       <c r="A1361" s="1" t="n">
@@ -45319,9 +45337,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1361" t="inlineStr"/>
-      <c r="H1361" t="inlineStr"/>
-      <c r="I1361" t="inlineStr"/>
+      <c r="G1361" s="1" t="n">
+        <v>46303.74037910163</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="I1361" t="n">
+        <v>-1.576404780066119</v>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" s="1" t="n">
@@ -45673,6 +45697,141 @@
       <c r="G1374" t="inlineStr"/>
       <c r="H1374" t="inlineStr"/>
       <c r="I1374" t="inlineStr"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>20.4435</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>18.4965</v>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="inlineStr"/>
+      <c r="I1375" t="inlineStr"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>62.43300000000001</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>56.48699999999999</v>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="inlineStr"/>
+      <c r="I1376" t="inlineStr"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>25.2105</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>22.8095</v>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr"/>
+      <c r="H1377" t="inlineStr"/>
+      <c r="I1377" t="inlineStr"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>16.254</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>14.706</v>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr"/>
+      <c r="H1378" t="inlineStr"/>
+      <c r="I1378" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>7.189</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>7.548450000000001</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>6.829549999999999</v>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr"/>
+      <c r="H1379" t="inlineStr"/>
+      <c r="I1379" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1379"/>
+  <dimension ref="A1:I1384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45206,7 +45206,7 @@
         </is>
       </c>
       <c r="G1357" s="1" t="n">
-        <v>46303.74037910163</v>
+        <v>46303.74037909722</v>
       </c>
       <c r="H1357" t="n">
         <v>5203</v>
@@ -45239,7 +45239,7 @@
         </is>
       </c>
       <c r="G1358" s="1" t="n">
-        <v>46303.74037910163</v>
+        <v>46303.74037909722</v>
       </c>
       <c r="H1358" t="n">
         <v>5582.5</v>
@@ -45305,7 +45305,7 @@
         </is>
       </c>
       <c r="G1360" s="1" t="n">
-        <v>46303.74037910163</v>
+        <v>46303.74037909722</v>
       </c>
       <c r="H1360" t="n">
         <v>19.08</v>
@@ -45338,7 +45338,7 @@
         </is>
       </c>
       <c r="G1361" s="1" t="n">
-        <v>46303.74037910163</v>
+        <v>46303.74037909722</v>
       </c>
       <c r="H1361" t="n">
         <v>39.95</v>
@@ -45370,9 +45370,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1362" t="inlineStr"/>
-      <c r="H1362" t="inlineStr"/>
-      <c r="I1362" t="inlineStr"/>
+      <c r="G1362" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>587.1</v>
+      </c>
+      <c r="I1362" t="n">
+        <v>2.353556485355648</v>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" s="1" t="n">
@@ -45397,9 +45403,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1363" t="inlineStr"/>
-      <c r="H1363" t="inlineStr"/>
-      <c r="I1363" t="inlineStr"/>
+      <c r="G1363" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="I1363" t="n">
+        <v>1.322614107883816</v>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" s="1" t="n">
@@ -45424,9 +45436,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1364" t="inlineStr"/>
-      <c r="H1364" t="inlineStr"/>
-      <c r="I1364" t="inlineStr"/>
+      <c r="G1364" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>54.135</v>
+      </c>
+      <c r="I1364" t="n">
+        <v>-0.3130466807844613</v>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" s="1" t="n">
@@ -45451,9 +45469,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1365" t="inlineStr"/>
-      <c r="H1365" t="inlineStr"/>
-      <c r="I1365" t="inlineStr"/>
+      <c r="G1365" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I1365" t="n">
+        <v>0.8284023668638877</v>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" s="1" t="n">
@@ -45478,9 +45502,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1366" t="inlineStr"/>
-      <c r="H1366" t="inlineStr"/>
-      <c r="I1366" t="inlineStr"/>
+      <c r="G1366" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="I1366" t="n">
+        <v>0.7772020725388711</v>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" s="1" t="n">
@@ -45505,9 +45535,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1367" t="inlineStr"/>
-      <c r="H1367" t="inlineStr"/>
-      <c r="I1367" t="inlineStr"/>
+      <c r="G1367" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>7.145</v>
+      </c>
+      <c r="I1367" t="n">
+        <v>-1.246988805441394</v>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" s="1" t="n">
@@ -45532,9 +45568,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1368" t="inlineStr"/>
-      <c r="H1368" t="inlineStr"/>
-      <c r="I1368" t="inlineStr"/>
+      <c r="G1368" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="I1368" t="n">
+        <v>-0.01026061974143763</v>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" s="1" t="n">
@@ -45559,9 +45601,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1369" t="inlineStr"/>
-      <c r="H1369" t="inlineStr"/>
-      <c r="I1369" t="inlineStr"/>
+      <c r="G1369" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="I1369" t="n">
+        <v>3.636058981233247</v>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" s="1" t="n">
@@ -45832,6 +45880,141 @@
       <c r="G1379" t="inlineStr"/>
       <c r="H1379" t="inlineStr"/>
       <c r="I1379" t="inlineStr"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>5633</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>5914.650000000001</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>5351.349999999999</v>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr"/>
+      <c r="H1380" t="inlineStr"/>
+      <c r="I1380" t="inlineStr"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>5206</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>5466.3</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>4945.7</v>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr"/>
+      <c r="H1381" t="inlineStr"/>
+      <c r="I1381" t="inlineStr"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>19.8555</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>17.9645</v>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr"/>
+      <c r="H1382" t="inlineStr"/>
+      <c r="I1382" t="inlineStr"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>77.07000000000001</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr"/>
+      <c r="H1383" t="inlineStr"/>
+      <c r="I1383" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>22.7955</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>20.6245</v>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr"/>
+      <c r="H1384" t="inlineStr"/>
+      <c r="I1384" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1384"/>
+  <dimension ref="A1:I1389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45371,7 +45371,7 @@
         </is>
       </c>
       <c r="G1362" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1362" t="n">
         <v>587.1</v>
@@ -45404,7 +45404,7 @@
         </is>
       </c>
       <c r="G1363" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1363" t="n">
         <v>0.3907</v>
@@ -45437,7 +45437,7 @@
         </is>
       </c>
       <c r="G1364" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1364" t="n">
         <v>54.135</v>
@@ -45470,7 +45470,7 @@
         </is>
       </c>
       <c r="G1365" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1365" t="n">
         <v>33.52</v>
@@ -45503,7 +45503,7 @@
         </is>
       </c>
       <c r="G1366" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1366" t="n">
         <v>19.15</v>
@@ -45536,7 +45536,7 @@
         </is>
       </c>
       <c r="G1367" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1367" t="n">
         <v>7.145</v>
@@ -45569,7 +45569,7 @@
         </is>
       </c>
       <c r="G1368" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1368" t="n">
         <v>97.47</v>
@@ -45602,7 +45602,7 @@
         </is>
       </c>
       <c r="G1369" s="1" t="n">
-        <v>46304.7288209574</v>
+        <v>46304.72882096065</v>
       </c>
       <c r="H1369" t="n">
         <v>115.02</v>
@@ -45634,9 +45634,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1370" t="inlineStr"/>
-      <c r="H1370" t="inlineStr"/>
-      <c r="I1370" t="inlineStr"/>
+      <c r="G1370" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>5988</v>
+      </c>
+      <c r="I1370" t="n">
+        <v>-7.16778523489933</v>
+      </c>
     </row>
     <row r="1371">
       <c r="A1371" s="1" t="n">
@@ -45661,9 +45667,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1371" t="inlineStr"/>
-      <c r="H1371" t="inlineStr"/>
-      <c r="I1371" t="inlineStr"/>
+      <c r="G1371" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>5349</v>
+      </c>
+      <c r="I1371" t="n">
+        <v>-2.667946257197697</v>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" s="1" t="n">
@@ -45688,9 +45700,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1372" t="inlineStr"/>
-      <c r="H1372" t="inlineStr"/>
-      <c r="I1372" t="inlineStr"/>
+      <c r="G1372" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>54.905</v>
+      </c>
+      <c r="I1372" t="n">
+        <v>1.320992092020128</v>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" s="1" t="n">
@@ -45715,9 +45733,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1373" t="inlineStr"/>
-      <c r="H1373" t="inlineStr"/>
-      <c r="I1373" t="inlineStr"/>
+      <c r="G1373" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1373" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="I1373" t="n">
+        <v>-0.43333333333333</v>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" s="1" t="n">
@@ -45742,9 +45766,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1374" t="inlineStr"/>
-      <c r="H1374" t="inlineStr"/>
-      <c r="I1374" t="inlineStr"/>
+      <c r="G1374" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="I1374" t="n">
+        <v>-1.641791044776111</v>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" s="1" t="n">
@@ -45769,9 +45799,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1375" t="inlineStr"/>
-      <c r="H1375" t="inlineStr"/>
-      <c r="I1375" t="inlineStr"/>
+      <c r="G1375" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="I1375" t="n">
+        <v>-5.033384694401646</v>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" s="1" t="n">
@@ -45796,9 +45832,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1376" t="inlineStr"/>
-      <c r="H1376" t="inlineStr"/>
-      <c r="I1376" t="inlineStr"/>
+      <c r="G1376" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="I1376" t="n">
+        <v>-1.345442314160775</v>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" s="1" t="n">
@@ -45823,9 +45865,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1377" t="inlineStr"/>
-      <c r="H1377" t="inlineStr"/>
-      <c r="I1377" t="inlineStr"/>
+      <c r="G1377" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="I1377" t="n">
+        <v>-2.665556018325685</v>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" s="1" t="n">
@@ -45850,9 +45898,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1378" t="inlineStr"/>
-      <c r="H1378" t="inlineStr"/>
-      <c r="I1378" t="inlineStr"/>
+      <c r="G1378" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="I1378" t="n">
+        <v>-5.749354005167962</v>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" s="1" t="n">
@@ -45877,9 +45931,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1379" t="inlineStr"/>
-      <c r="H1379" t="inlineStr"/>
-      <c r="I1379" t="inlineStr"/>
+      <c r="G1379" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>7.461</v>
+      </c>
+      <c r="I1379" t="n">
+        <v>-3.783558213937964</v>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" s="1" t="n">
@@ -45904,9 +45964,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1380" t="inlineStr"/>
-      <c r="H1380" t="inlineStr"/>
-      <c r="I1380" t="inlineStr"/>
+      <c r="G1380" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>5988</v>
+      </c>
+      <c r="I1380" t="n">
+        <v>-6.302148056097994</v>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" s="1" t="n">
@@ -45931,9 +45997,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1381" t="inlineStr"/>
-      <c r="H1381" t="inlineStr"/>
-      <c r="I1381" t="inlineStr"/>
+      <c r="G1381" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>5349</v>
+      </c>
+      <c r="I1381" t="n">
+        <v>-2.746830580099885</v>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" s="1" t="n">
@@ -45958,9 +46030,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1382" t="inlineStr"/>
-      <c r="H1382" t="inlineStr"/>
-      <c r="I1382" t="inlineStr"/>
+      <c r="G1382" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="I1382" t="n">
+        <v>-8.143839238498146</v>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" s="1" t="n">
@@ -45985,9 +46063,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1383" t="inlineStr"/>
-      <c r="H1383" t="inlineStr"/>
-      <c r="I1383" t="inlineStr"/>
+      <c r="G1383" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>75.62</v>
+      </c>
+      <c r="I1383" t="n">
+        <v>-3.024523160762941</v>
+      </c>
     </row>
     <row r="1384">
       <c r="A1384" s="1" t="n">
@@ -46012,9 +46096,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1384" t="inlineStr"/>
-      <c r="H1384" t="inlineStr"/>
-      <c r="I1384" t="inlineStr"/>
+      <c r="G1384" s="1" t="n">
+        <v>46307.82892078701</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>22.155</v>
+      </c>
+      <c r="I1384" t="n">
+        <v>-2.049746660525105</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>17.5245</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>15.8555</v>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr"/>
+      <c r="H1385" t="inlineStr"/>
+      <c r="I1385" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>401.2575</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>363.0425</v>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr"/>
+      <c r="H1386" t="inlineStr"/>
+      <c r="I1386" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>91</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr"/>
+      <c r="H1387" t="inlineStr"/>
+      <c r="I1387" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>619</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>649.95</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>588.05</v>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr"/>
+      <c r="H1388" t="inlineStr"/>
+      <c r="I1388" t="inlineStr"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>6164.5</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>6472.725</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>5856.275</v>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr"/>
+      <c r="H1389" t="inlineStr"/>
+      <c r="I1389" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1389"/>
+  <dimension ref="A1:I1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45635,7 +45635,7 @@
         </is>
       </c>
       <c r="G1370" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1370" t="n">
         <v>5988</v>
@@ -45668,7 +45668,7 @@
         </is>
       </c>
       <c r="G1371" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1371" t="n">
         <v>5349</v>
@@ -45701,7 +45701,7 @@
         </is>
       </c>
       <c r="G1372" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1372" t="n">
         <v>54.905</v>
@@ -45734,7 +45734,7 @@
         </is>
       </c>
       <c r="G1373" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1373" t="n">
         <v>60.26</v>
@@ -45767,7 +45767,7 @@
         </is>
       </c>
       <c r="G1374" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1374" t="n">
         <v>40.86</v>
@@ -45800,7 +45800,7 @@
         </is>
       </c>
       <c r="G1375" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1375" t="n">
         <v>20.45</v>
@@ -45833,7 +45833,7 @@
         </is>
       </c>
       <c r="G1376" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1376" t="n">
         <v>60.26</v>
@@ -45866,7 +45866,7 @@
         </is>
       </c>
       <c r="G1377" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1377" t="n">
         <v>24.65</v>
@@ -45899,7 +45899,7 @@
         </is>
       </c>
       <c r="G1378" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1378" t="n">
         <v>16.37</v>
@@ -45932,7 +45932,7 @@
         </is>
       </c>
       <c r="G1379" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1379" t="n">
         <v>7.461</v>
@@ -45965,7 +45965,7 @@
         </is>
       </c>
       <c r="G1380" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1380" t="n">
         <v>5988</v>
@@ -45998,7 +45998,7 @@
         </is>
       </c>
       <c r="G1381" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1381" t="n">
         <v>5349</v>
@@ -46031,7 +46031,7 @@
         </is>
       </c>
       <c r="G1382" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1382" t="n">
         <v>20.45</v>
@@ -46064,7 +46064,7 @@
         </is>
       </c>
       <c r="G1383" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1383" t="n">
         <v>75.62</v>
@@ -46097,7 +46097,7 @@
         </is>
       </c>
       <c r="G1384" s="1" t="n">
-        <v>46307.82892078701</v>
+        <v>46307.82892078704</v>
       </c>
       <c r="H1384" t="n">
         <v>22.155</v>
@@ -46210,9 +46210,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1388" t="inlineStr"/>
-      <c r="H1388" t="inlineStr"/>
-      <c r="I1388" t="inlineStr"/>
+      <c r="G1388" s="1" t="n">
+        <v>46308.7586239597</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>588.05</v>
+      </c>
+      <c r="I1388" t="n">
+        <v>5.000000000000007</v>
+      </c>
     </row>
     <row r="1389">
       <c r="A1389" s="1" t="n">
@@ -46240,6 +46246,141 @@
       <c r="G1389" t="inlineStr"/>
       <c r="H1389" t="inlineStr"/>
       <c r="I1389" t="inlineStr"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>21.4725</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>19.4275</v>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr"/>
+      <c r="H1390" t="inlineStr"/>
+      <c r="I1390" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>5983</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>6282.150000000001</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>5683.849999999999</v>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr"/>
+      <c r="H1391" t="inlineStr"/>
+      <c r="I1391" t="inlineStr"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>5311</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>5576.55</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>5045.45</v>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr"/>
+      <c r="H1392" t="inlineStr"/>
+      <c r="I1392" t="inlineStr"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>MGNT</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>1736</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>1822.8</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>1649.2</v>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="inlineStr"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>41.115</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>43.17075000000001</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>39.05925</v>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr"/>
+      <c r="H1394" t="inlineStr"/>
+      <c r="I1394" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1394"/>
+  <dimension ref="A1:I1404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46211,7 +46211,7 @@
         </is>
       </c>
       <c r="G1388" s="1" t="n">
-        <v>46308.7586239597</v>
+        <v>46308.75862395833</v>
       </c>
       <c r="H1388" t="n">
         <v>588.05</v>
@@ -46381,6 +46381,276 @@
       <c r="G1394" t="inlineStr"/>
       <c r="H1394" t="inlineStr"/>
       <c r="I1394" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>SBER</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>272.2415</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>309.4956</v>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr"/>
+      <c r="H1395" t="inlineStr"/>
+      <c r="I1395" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>0.464184</v>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr"/>
+      <c r="H1396" t="inlineStr"/>
+      <c r="I1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>33.611</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>38.21040000000001</v>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="inlineStr"/>
+      <c r="I1397" t="inlineStr"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>5444</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>5171.8</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>5879.52</v>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="inlineStr"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>CHMF</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>724.8</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>688.5599999999999</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>782.784</v>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr"/>
+      <c r="H1399" t="inlineStr"/>
+      <c r="I1399" t="inlineStr"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>45.234</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>40.92599999999999</v>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr"/>
+      <c r="H1400" t="inlineStr"/>
+      <c r="I1400" t="inlineStr"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>17.4825</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>15.8175</v>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr"/>
+      <c r="H1401" t="inlineStr"/>
+      <c r="I1401" t="inlineStr"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>26.229</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>23.731</v>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr"/>
+      <c r="H1402" t="inlineStr"/>
+      <c r="I1402" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>41.295</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>43.35975000000001</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>39.23025</v>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr"/>
+      <c r="H1403" t="inlineStr"/>
+      <c r="I1403" t="inlineStr"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>97.125</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>87.875</v>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr"/>
+      <c r="H1404" t="inlineStr"/>
+      <c r="I1404" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1404"/>
+  <dimension ref="A1:I1410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46129,9 +46129,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1385" t="inlineStr"/>
-      <c r="H1385" t="inlineStr"/>
-      <c r="I1385" t="inlineStr"/>
+      <c r="G1385" s="1" t="n">
+        <v>46310.65659430043</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>16.575</v>
+      </c>
+      <c r="I1385" t="n">
+        <v>0.6890353505092989</v>
+      </c>
     </row>
     <row r="1386">
       <c r="A1386" s="1" t="n">
@@ -46156,9 +46162,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1386" t="inlineStr"/>
-      <c r="H1386" t="inlineStr"/>
-      <c r="I1386" t="inlineStr"/>
+      <c r="G1386" s="1" t="n">
+        <v>46310.65659430043</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="I1386" t="n">
+        <v>2.185005887740407</v>
+      </c>
     </row>
     <row r="1387">
       <c r="A1387" s="1" t="n">
@@ -46183,9 +46195,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1387" t="inlineStr"/>
-      <c r="H1387" t="inlineStr"/>
-      <c r="I1387" t="inlineStr"/>
+      <c r="G1387" s="1" t="n">
+        <v>46310.65659430043</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="I1387" t="n">
+        <v>1.538461538461545</v>
+      </c>
     </row>
     <row r="1388">
       <c r="A1388" s="1" t="n">
@@ -46243,9 +46261,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1389" t="inlineStr"/>
-      <c r="H1389" t="inlineStr"/>
-      <c r="I1389" t="inlineStr"/>
+      <c r="G1389" s="1" t="n">
+        <v>46310.65659430043</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>6043.5</v>
+      </c>
+      <c r="I1389" t="n">
+        <v>1.962851812799091</v>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" s="1" t="n">
@@ -46324,9 +46348,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1392" t="inlineStr"/>
-      <c r="H1392" t="inlineStr"/>
-      <c r="I1392" t="inlineStr"/>
+      <c r="G1392" s="1" t="n">
+        <v>46310.65659430043</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>5576.55</v>
+      </c>
+      <c r="I1392" t="n">
+        <v>-5.000000000000004</v>
+      </c>
     </row>
     <row r="1393">
       <c r="A1393" s="1" t="n">
@@ -46651,6 +46681,168 @@
       <c r="G1404" t="inlineStr"/>
       <c r="H1404" t="inlineStr"/>
       <c r="I1404" t="inlineStr"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>5206</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>5918.400000000001</v>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr"/>
+      <c r="H1405" t="inlineStr"/>
+      <c r="I1405" t="inlineStr"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr"/>
+      <c r="H1406" t="inlineStr"/>
+      <c r="I1406" t="inlineStr"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>24.255</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>25.46775</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>23.04225</v>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr"/>
+      <c r="H1407" t="inlineStr"/>
+      <c r="I1407" t="inlineStr"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>94.44750000000001</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>85.4525</v>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr"/>
+      <c r="H1408" t="inlineStr"/>
+      <c r="I1408" t="inlineStr"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr"/>
+      <c r="H1409" t="inlineStr"/>
+      <c r="I1409" t="inlineStr"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>115.88</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>121.674</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>110.086</v>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr"/>
+      <c r="H1410" t="inlineStr"/>
+      <c r="I1410" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
